--- a/diseases/d059/2010-2014.xlsx
+++ b/diseases/d059/2010-2014.xlsx
@@ -29064,17 +29064,15 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
       <c r="Q199" t="n">
         <v>0</v>
       </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U199" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -29082,7 +29080,7 @@
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
@@ -29092,12 +29090,7 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr">
@@ -29107,11 +29100,6 @@
       </c>
       <c r="AT199" t="n">
         <v>1</v>
-      </c>
-      <c r="AU199" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
@@ -29373,17 +29361,15 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
       <c r="Q201" t="n">
         <v>0</v>
       </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U201" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -29391,7 +29377,7 @@
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
@@ -29401,12 +29387,7 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr">
@@ -29416,11 +29397,6 @@
       </c>
       <c r="AT201" t="n">
         <v>1</v>
-      </c>
-      <c r="AU201" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
@@ -29682,17 +29658,15 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
       <c r="Q203" t="n">
         <v>0</v>
       </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U203" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -29700,7 +29674,7 @@
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
@@ -29710,12 +29684,7 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr">
@@ -29725,11 +29694,6 @@
       </c>
       <c r="AT203" t="n">
         <v>1</v>
-      </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
@@ -30264,17 +30228,15 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
       <c r="Q207" t="n">
         <v>0</v>
       </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U207" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -30282,7 +30244,7 @@
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
@@ -30292,12 +30254,7 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr">
@@ -30307,11 +30264,6 @@
       </c>
       <c r="AT207" t="n">
         <v>1</v>
-      </c>
-      <c r="AU207" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
@@ -30573,17 +30525,15 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
       <c r="Q209" t="n">
         <v>0</v>
       </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U209" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -30591,7 +30541,7 @@
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
@@ -30601,12 +30551,7 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
@@ -30616,11 +30561,6 @@
       </c>
       <c r="AT209" t="n">
         <v>1</v>
-      </c>
-      <c r="AU209" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
@@ -30882,17 +30822,15 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
       <c r="Q211" t="n">
         <v>0</v>
       </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U211" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -30900,7 +30838,7 @@
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -30910,12 +30848,7 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ211" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
@@ -30925,11 +30858,6 @@
       </c>
       <c r="AT211" t="n">
         <v>1</v>
-      </c>
-      <c r="AU211" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
@@ -31191,17 +31119,15 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
       <c r="Q213" t="n">
         <v>0</v>
       </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U213" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -31209,7 +31135,7 @@
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
@@ -31219,12 +31145,7 @@
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ213" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr">
@@ -31234,11 +31155,6 @@
       </c>
       <c r="AT213" t="n">
         <v>1</v>
-      </c>
-      <c r="AU213" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
@@ -31773,17 +31689,15 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
       <c r="Q217" t="n">
         <v>0</v>
       </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U217" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -31791,7 +31705,7 @@
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -31801,12 +31715,7 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ217" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr">
@@ -31816,11 +31725,6 @@
       </c>
       <c r="AT217" t="n">
         <v>1</v>
-      </c>
-      <c r="AU217" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
@@ -32082,17 +31986,15 @@
       <c r="O219" t="n">
         <v>0</v>
       </c>
+      <c r="P219" t="n">
+        <v>0</v>
+      </c>
       <c r="Q219" t="n">
         <v>0</v>
       </c>
       <c r="R219" t="n">
         <v>0</v>
       </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U219" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -32100,7 +32002,7 @@
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
@@ -32110,12 +32012,7 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ219" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr">
@@ -32125,11 +32022,6 @@
       </c>
       <c r="AT219" t="n">
         <v>1</v>
-      </c>
-      <c r="AU219" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
@@ -32391,17 +32283,15 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
       <c r="Q221" t="n">
         <v>0</v>
       </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U221" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -32409,7 +32299,7 @@
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
@@ -32419,12 +32309,7 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ221" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
@@ -32434,11 +32319,6 @@
       </c>
       <c r="AT221" t="n">
         <v>1</v>
-      </c>
-      <c r="AU221" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
@@ -32700,17 +32580,15 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
       <c r="Q223" t="n">
         <v>0</v>
       </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U223" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -32718,7 +32596,7 @@
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
@@ -32728,12 +32606,7 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ223" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
@@ -32743,11 +32616,6 @@
       </c>
       <c r="AT223" t="n">
         <v>1</v>
-      </c>
-      <c r="AU223" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
@@ -33009,17 +32877,15 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
       <c r="Q225" t="n">
         <v>0</v>
       </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U225" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -33027,7 +32893,7 @@
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
@@ -33037,12 +32903,7 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ225" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
@@ -33052,11 +32913,6 @@
       </c>
       <c r="AT225" t="n">
         <v>1</v>
-      </c>
-      <c r="AU225" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
@@ -33591,17 +33447,15 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
       <c r="Q229" t="n">
         <v>0</v>
       </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U229" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -33609,7 +33463,7 @@
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
@@ -33619,12 +33473,7 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ229" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
@@ -33634,11 +33483,6 @@
       </c>
       <c r="AT229" t="n">
         <v>1</v>
-      </c>
-      <c r="AU229" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
@@ -33900,17 +33744,15 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
+      <c r="P231" t="n">
+        <v>0</v>
+      </c>
       <c r="Q231" t="n">
         <v>0</v>
       </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U231" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -33918,7 +33760,7 @@
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
@@ -33928,12 +33770,7 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
@@ -33943,11 +33780,6 @@
       </c>
       <c r="AT231" t="n">
         <v>1</v>
-      </c>
-      <c r="AU231" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
@@ -34209,17 +34041,15 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
       <c r="Q233" t="n">
         <v>0</v>
       </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U233" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -34227,7 +34057,7 @@
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
@@ -34237,12 +34067,7 @@
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ233" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr">
@@ -34252,11 +34077,6 @@
       </c>
       <c r="AT233" t="n">
         <v>1</v>
-      </c>
-      <c r="AU233" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
@@ -34518,17 +34338,15 @@
       <c r="O235" t="n">
         <v>0</v>
       </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
       <c r="Q235" t="n">
         <v>0</v>
       </c>
       <c r="R235" t="n">
         <v>0</v>
       </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U235" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -34536,7 +34354,7 @@
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
@@ -34546,12 +34364,7 @@
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
@@ -34561,11 +34374,6 @@
       </c>
       <c r="AT235" t="n">
         <v>1</v>
-      </c>
-      <c r="AU235" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
@@ -39960,17 +39768,15 @@
       <c r="O272" t="n">
         <v>0</v>
       </c>
+      <c r="P272" t="n">
+        <v>0</v>
+      </c>
       <c r="Q272" t="n">
         <v>0</v>
       </c>
       <c r="R272" t="n">
         <v>0</v>
       </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U272" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -39978,7 +39784,7 @@
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO272" t="inlineStr">
@@ -39988,12 +39794,7 @@
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ272" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS272" t="inlineStr">
@@ -40003,11 +39804,6 @@
       </c>
       <c r="AT272" t="n">
         <v>1</v>
-      </c>
-      <c r="AU272" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
@@ -40269,17 +40065,15 @@
       <c r="O274" t="n">
         <v>0</v>
       </c>
+      <c r="P274" t="n">
+        <v>0</v>
+      </c>
       <c r="Q274" t="n">
         <v>0</v>
       </c>
       <c r="R274" t="n">
         <v>0</v>
       </c>
-      <c r="S274" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U274" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -40287,7 +40081,7 @@
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO274" t="inlineStr">
@@ -40297,12 +40091,7 @@
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ274" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS274" t="inlineStr">
@@ -40312,11 +40101,6 @@
       </c>
       <c r="AT274" t="n">
         <v>1</v>
-      </c>
-      <c r="AU274" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
@@ -40578,17 +40362,15 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
+      <c r="P276" t="n">
+        <v>0</v>
+      </c>
       <c r="Q276" t="n">
         <v>0</v>
       </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
-      <c r="S276" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U276" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -40596,7 +40378,7 @@
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO276" t="inlineStr">
@@ -40606,12 +40388,7 @@
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ276" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS276" t="inlineStr">
@@ -40621,11 +40398,6 @@
       </c>
       <c r="AT276" t="n">
         <v>1</v>
-      </c>
-      <c r="AU276" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV276" t="inlineStr">
         <is>
@@ -40887,17 +40659,15 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
       <c r="Q278" t="n">
         <v>0</v>
       </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
-      <c r="S278" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U278" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -40905,7 +40675,7 @@
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO278" t="inlineStr">
@@ -40915,12 +40685,7 @@
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ278" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS278" t="inlineStr">
@@ -40930,11 +40695,6 @@
       </c>
       <c r="AT278" t="n">
         <v>1</v>
-      </c>
-      <c r="AU278" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
@@ -41334,17 +41094,15 @@
       <c r="O281" t="n">
         <v>0</v>
       </c>
+      <c r="P281" t="n">
+        <v>0</v>
+      </c>
       <c r="Q281" t="n">
         <v>0</v>
       </c>
       <c r="R281" t="n">
         <v>0</v>
       </c>
-      <c r="S281" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U281" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -41352,7 +41110,7 @@
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO281" t="inlineStr">
@@ -41362,12 +41120,7 @@
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ281" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS281" t="inlineStr">
@@ -41377,11 +41130,6 @@
       </c>
       <c r="AT281" t="n">
         <v>1</v>
-      </c>
-      <c r="AU281" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>
@@ -41778,17 +41526,15 @@
       <c r="O284" t="n">
         <v>0</v>
       </c>
+      <c r="P284" t="n">
+        <v>0</v>
+      </c>
       <c r="Q284" t="n">
         <v>0</v>
       </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
-      <c r="S284" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U284" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -41796,7 +41542,7 @@
       </c>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO284" t="inlineStr">
@@ -41806,12 +41552,7 @@
       </c>
       <c r="AP284" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ284" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS284" t="inlineStr">
@@ -41821,11 +41562,6 @@
       </c>
       <c r="AT284" t="n">
         <v>1</v>
-      </c>
-      <c r="AU284" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV284" t="inlineStr">
         <is>
@@ -42087,17 +41823,15 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
+      <c r="P286" t="n">
+        <v>0</v>
+      </c>
       <c r="Q286" t="n">
         <v>0</v>
       </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
-      <c r="S286" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U286" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -42105,7 +41839,7 @@
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO286" t="inlineStr">
@@ -42115,12 +41849,7 @@
       </c>
       <c r="AP286" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ286" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS286" t="inlineStr">
@@ -42130,11 +41859,6 @@
       </c>
       <c r="AT286" t="n">
         <v>1</v>
-      </c>
-      <c r="AU286" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV286" t="inlineStr">
         <is>
@@ -42396,17 +42120,15 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
+      <c r="P288" t="n">
+        <v>0</v>
+      </c>
       <c r="Q288" t="n">
         <v>0</v>
       </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
-      <c r="S288" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U288" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -42414,7 +42136,7 @@
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO288" t="inlineStr">
@@ -42424,12 +42146,7 @@
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ288" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS288" t="inlineStr">
@@ -42439,11 +42156,6 @@
       </c>
       <c r="AT288" t="n">
         <v>1</v>
-      </c>
-      <c r="AU288" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
@@ -42843,17 +42555,15 @@
       <c r="O291" t="n">
         <v>0</v>
       </c>
+      <c r="P291" t="n">
+        <v>0</v>
+      </c>
       <c r="Q291" t="n">
         <v>0</v>
       </c>
       <c r="R291" t="n">
         <v>0</v>
       </c>
-      <c r="S291" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U291" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -42861,7 +42571,7 @@
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO291" t="inlineStr">
@@ -42871,12 +42581,7 @@
       </c>
       <c r="AP291" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ291" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS291" t="inlineStr">
@@ -42886,11 +42591,6 @@
       </c>
       <c r="AT291" t="n">
         <v>1</v>
-      </c>
-      <c r="AU291" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV291" t="inlineStr">
         <is>
@@ -43287,17 +42987,15 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
+      <c r="P294" t="n">
+        <v>0</v>
+      </c>
       <c r="Q294" t="n">
         <v>0</v>
       </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
-      <c r="S294" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U294" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -43305,7 +43003,7 @@
       </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO294" t="inlineStr">
@@ -43315,12 +43013,7 @@
       </c>
       <c r="AP294" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ294" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS294" t="inlineStr">
@@ -43330,11 +43023,6 @@
       </c>
       <c r="AT294" t="n">
         <v>1</v>
-      </c>
-      <c r="AU294" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV294" t="inlineStr">
         <is>
@@ -43596,17 +43284,15 @@
       <c r="O296" t="n">
         <v>0</v>
       </c>
+      <c r="P296" t="n">
+        <v>0</v>
+      </c>
       <c r="Q296" t="n">
         <v>0</v>
       </c>
       <c r="R296" t="n">
         <v>0</v>
       </c>
-      <c r="S296" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U296" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -43614,7 +43300,7 @@
       </c>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO296" t="inlineStr">
@@ -43624,12 +43310,7 @@
       </c>
       <c r="AP296" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ296" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS296" t="inlineStr">
@@ -43639,11 +43320,6 @@
       </c>
       <c r="AT296" t="n">
         <v>1</v>
-      </c>
-      <c r="AU296" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV296" t="inlineStr">
         <is>
@@ -43905,17 +43581,15 @@
       <c r="O298" t="n">
         <v>0</v>
       </c>
+      <c r="P298" t="n">
+        <v>0</v>
+      </c>
       <c r="Q298" t="n">
         <v>0</v>
       </c>
       <c r="R298" t="n">
         <v>0</v>
       </c>
-      <c r="S298" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U298" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -43923,7 +43597,7 @@
       </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO298" t="inlineStr">
@@ -43933,12 +43607,7 @@
       </c>
       <c r="AP298" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ298" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS298" t="inlineStr">
@@ -43948,11 +43617,6 @@
       </c>
       <c r="AT298" t="n">
         <v>1</v>
-      </c>
-      <c r="AU298" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV298" t="inlineStr">
         <is>
@@ -44214,17 +43878,15 @@
       <c r="O300" t="n">
         <v>0</v>
       </c>
+      <c r="P300" t="n">
+        <v>0</v>
+      </c>
       <c r="Q300" t="n">
         <v>0</v>
       </c>
       <c r="R300" t="n">
         <v>0</v>
       </c>
-      <c r="S300" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U300" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -44232,7 +43894,7 @@
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO300" t="inlineStr">
@@ -44242,12 +43904,7 @@
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ300" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS300" t="inlineStr">
@@ -44257,11 +43914,6 @@
       </c>
       <c r="AT300" t="n">
         <v>1</v>
-      </c>
-      <c r="AU300" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV300" t="inlineStr">
         <is>
@@ -44796,17 +44448,15 @@
       <c r="O304" t="n">
         <v>0</v>
       </c>
+      <c r="P304" t="n">
+        <v>0</v>
+      </c>
       <c r="Q304" t="n">
         <v>0</v>
       </c>
       <c r="R304" t="n">
         <v>0</v>
       </c>
-      <c r="S304" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U304" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -44814,7 +44464,7 @@
       </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO304" t="inlineStr">
@@ -44824,12 +44474,7 @@
       </c>
       <c r="AP304" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ304" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS304" t="inlineStr">
@@ -44839,11 +44484,6 @@
       </c>
       <c r="AT304" t="n">
         <v>1</v>
-      </c>
-      <c r="AU304" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV304" t="inlineStr">
         <is>
@@ -45105,17 +44745,15 @@
       <c r="O306" t="n">
         <v>0</v>
       </c>
+      <c r="P306" t="n">
+        <v>0</v>
+      </c>
       <c r="Q306" t="n">
         <v>0</v>
       </c>
       <c r="R306" t="n">
         <v>0</v>
       </c>
-      <c r="S306" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U306" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -45123,7 +44761,7 @@
       </c>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO306" t="inlineStr">
@@ -45133,12 +44771,7 @@
       </c>
       <c r="AP306" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ306" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS306" t="inlineStr">
@@ -45148,11 +44781,6 @@
       </c>
       <c r="AT306" t="n">
         <v>1</v>
-      </c>
-      <c r="AU306" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV306" t="inlineStr">
         <is>
@@ -45414,17 +45042,15 @@
       <c r="O308" t="n">
         <v>0</v>
       </c>
+      <c r="P308" t="n">
+        <v>0</v>
+      </c>
       <c r="Q308" t="n">
         <v>0</v>
       </c>
       <c r="R308" t="n">
         <v>0</v>
       </c>
-      <c r="S308" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U308" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -45432,7 +45058,7 @@
       </c>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO308" t="inlineStr">
@@ -45442,12 +45068,7 @@
       </c>
       <c r="AP308" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ308" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS308" t="inlineStr">
@@ -45457,11 +45078,6 @@
       </c>
       <c r="AT308" t="n">
         <v>1</v>
-      </c>
-      <c r="AU308" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV308" t="inlineStr">
         <is>
@@ -45723,17 +45339,15 @@
       <c r="O310" t="n">
         <v>0</v>
       </c>
+      <c r="P310" t="n">
+        <v>0</v>
+      </c>
       <c r="Q310" t="n">
         <v>0</v>
       </c>
       <c r="R310" t="n">
         <v>0</v>
       </c>
-      <c r="S310" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U310" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -45741,7 +45355,7 @@
       </c>
       <c r="AA310" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO310" t="inlineStr">
@@ -45751,12 +45365,7 @@
       </c>
       <c r="AP310" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ310" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS310" t="inlineStr">
@@ -45766,11 +45375,6 @@
       </c>
       <c r="AT310" t="n">
         <v>1</v>
-      </c>
-      <c r="AU310" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV310" t="inlineStr">
         <is>
@@ -46305,17 +45909,15 @@
       <c r="O314" t="n">
         <v>0</v>
       </c>
+      <c r="P314" t="n">
+        <v>0</v>
+      </c>
       <c r="Q314" t="n">
         <v>0</v>
       </c>
       <c r="R314" t="n">
         <v>0</v>
       </c>
-      <c r="S314" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U314" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -46323,7 +45925,7 @@
       </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO314" t="inlineStr">
@@ -46333,12 +45935,7 @@
       </c>
       <c r="AP314" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ314" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS314" t="inlineStr">
@@ -46348,11 +45945,6 @@
       </c>
       <c r="AT314" t="n">
         <v>1</v>
-      </c>
-      <c r="AU314" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV314" t="inlineStr">
         <is>
@@ -46614,17 +46206,15 @@
       <c r="O316" t="n">
         <v>0</v>
       </c>
+      <c r="P316" t="n">
+        <v>0</v>
+      </c>
       <c r="Q316" t="n">
         <v>0</v>
       </c>
       <c r="R316" t="n">
         <v>0</v>
       </c>
-      <c r="S316" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U316" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -46632,7 +46222,7 @@
       </c>
       <c r="AA316" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO316" t="inlineStr">
@@ -46642,12 +46232,7 @@
       </c>
       <c r="AP316" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ316" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS316" t="inlineStr">
@@ -46657,11 +46242,6 @@
       </c>
       <c r="AT316" t="n">
         <v>1</v>
-      </c>
-      <c r="AU316" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV316" t="inlineStr">
         <is>
@@ -46923,17 +46503,15 @@
       <c r="O318" t="n">
         <v>0</v>
       </c>
+      <c r="P318" t="n">
+        <v>0</v>
+      </c>
       <c r="Q318" t="n">
         <v>0</v>
       </c>
       <c r="R318" t="n">
         <v>0</v>
       </c>
-      <c r="S318" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U318" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -46941,7 +46519,7 @@
       </c>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO318" t="inlineStr">
@@ -46951,12 +46529,7 @@
       </c>
       <c r="AP318" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ318" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS318" t="inlineStr">
@@ -46966,11 +46539,6 @@
       </c>
       <c r="AT318" t="n">
         <v>1</v>
-      </c>
-      <c r="AU318" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV318" t="inlineStr">
         <is>
@@ -47232,17 +46800,15 @@
       <c r="O320" t="n">
         <v>0</v>
       </c>
+      <c r="P320" t="n">
+        <v>0</v>
+      </c>
       <c r="Q320" t="n">
         <v>0</v>
       </c>
       <c r="R320" t="n">
         <v>0</v>
       </c>
-      <c r="S320" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U320" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -47250,7 +46816,7 @@
       </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO320" t="inlineStr">
@@ -47260,12 +46826,7 @@
       </c>
       <c r="AP320" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ320" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS320" t="inlineStr">
@@ -47275,11 +46836,6 @@
       </c>
       <c r="AT320" t="n">
         <v>1</v>
-      </c>
-      <c r="AU320" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV320" t="inlineStr">
         <is>
@@ -47541,17 +47097,15 @@
       <c r="O322" t="n">
         <v>0</v>
       </c>
+      <c r="P322" t="n">
+        <v>0</v>
+      </c>
       <c r="Q322" t="n">
         <v>0</v>
       </c>
       <c r="R322" t="n">
         <v>0</v>
       </c>
-      <c r="S322" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U322" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -47559,7 +47113,7 @@
       </c>
       <c r="AA322" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO322" t="inlineStr">
@@ -47569,12 +47123,7 @@
       </c>
       <c r="AP322" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ322" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS322" t="inlineStr">
@@ -47584,11 +47133,6 @@
       </c>
       <c r="AT322" t="n">
         <v>1</v>
-      </c>
-      <c r="AU322" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV322" t="inlineStr">
         <is>
@@ -48123,17 +47667,15 @@
       <c r="O326" t="n">
         <v>0</v>
       </c>
+      <c r="P326" t="n">
+        <v>0</v>
+      </c>
       <c r="Q326" t="n">
         <v>0</v>
       </c>
       <c r="R326" t="n">
         <v>0</v>
       </c>
-      <c r="S326" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U326" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -48141,7 +47683,7 @@
       </c>
       <c r="AA326" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO326" t="inlineStr">
@@ -48151,12 +47693,7 @@
       </c>
       <c r="AP326" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ326" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS326" t="inlineStr">
@@ -48166,11 +47703,6 @@
       </c>
       <c r="AT326" t="n">
         <v>1</v>
-      </c>
-      <c r="AU326" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV326" t="inlineStr">
         <is>
@@ -48432,17 +47964,15 @@
       <c r="O328" t="n">
         <v>0</v>
       </c>
+      <c r="P328" t="n">
+        <v>0</v>
+      </c>
       <c r="Q328" t="n">
         <v>0</v>
       </c>
       <c r="R328" t="n">
         <v>0</v>
       </c>
-      <c r="S328" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U328" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -48450,7 +47980,7 @@
       </c>
       <c r="AA328" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO328" t="inlineStr">
@@ -48460,12 +47990,7 @@
       </c>
       <c r="AP328" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ328" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS328" t="inlineStr">
@@ -48475,11 +48000,6 @@
       </c>
       <c r="AT328" t="n">
         <v>1</v>
-      </c>
-      <c r="AU328" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV328" t="inlineStr">
         <is>
@@ -48741,17 +48261,15 @@
       <c r="O330" t="n">
         <v>0</v>
       </c>
+      <c r="P330" t="n">
+        <v>0</v>
+      </c>
       <c r="Q330" t="n">
         <v>0</v>
       </c>
       <c r="R330" t="n">
         <v>0</v>
       </c>
-      <c r="S330" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U330" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -48759,7 +48277,7 @@
       </c>
       <c r="AA330" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO330" t="inlineStr">
@@ -48769,12 +48287,7 @@
       </c>
       <c r="AP330" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ330" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS330" t="inlineStr">
@@ -48784,11 +48297,6 @@
       </c>
       <c r="AT330" t="n">
         <v>1</v>
-      </c>
-      <c r="AU330" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV330" t="inlineStr">
         <is>
@@ -49050,17 +48558,15 @@
       <c r="O332" t="n">
         <v>0</v>
       </c>
+      <c r="P332" t="n">
+        <v>0</v>
+      </c>
       <c r="Q332" t="n">
         <v>0</v>
       </c>
       <c r="R332" t="n">
         <v>0</v>
       </c>
-      <c r="S332" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U332" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -49068,7 +48574,7 @@
       </c>
       <c r="AA332" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO332" t="inlineStr">
@@ -49078,12 +48584,7 @@
       </c>
       <c r="AP332" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ332" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS332" t="inlineStr">
@@ -49093,11 +48594,6 @@
       </c>
       <c r="AT332" t="n">
         <v>1</v>
-      </c>
-      <c r="AU332" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV332" t="inlineStr">
         <is>
@@ -49632,17 +49128,15 @@
       <c r="O336" t="n">
         <v>0</v>
       </c>
+      <c r="P336" t="n">
+        <v>0</v>
+      </c>
       <c r="Q336" t="n">
         <v>0</v>
       </c>
       <c r="R336" t="n">
         <v>0</v>
       </c>
-      <c r="S336" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U336" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -49650,7 +49144,7 @@
       </c>
       <c r="AA336" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO336" t="inlineStr">
@@ -49660,12 +49154,7 @@
       </c>
       <c r="AP336" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ336" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS336" t="inlineStr">
@@ -49675,11 +49164,6 @@
       </c>
       <c r="AT336" t="n">
         <v>1</v>
-      </c>
-      <c r="AU336" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV336" t="inlineStr">
         <is>
@@ -49941,17 +49425,15 @@
       <c r="O338" t="n">
         <v>0</v>
       </c>
+      <c r="P338" t="n">
+        <v>0</v>
+      </c>
       <c r="Q338" t="n">
         <v>0</v>
       </c>
       <c r="R338" t="n">
         <v>0</v>
       </c>
-      <c r="S338" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U338" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -49959,7 +49441,7 @@
       </c>
       <c r="AA338" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO338" t="inlineStr">
@@ -49969,12 +49451,7 @@
       </c>
       <c r="AP338" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ338" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS338" t="inlineStr">
@@ -49984,11 +49461,6 @@
       </c>
       <c r="AT338" t="n">
         <v>1</v>
-      </c>
-      <c r="AU338" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV338" t="inlineStr">
         <is>
@@ -50250,17 +49722,15 @@
       <c r="O340" t="n">
         <v>0</v>
       </c>
+      <c r="P340" t="n">
+        <v>0</v>
+      </c>
       <c r="Q340" t="n">
         <v>0</v>
       </c>
       <c r="R340" t="n">
         <v>0</v>
       </c>
-      <c r="S340" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U340" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -50268,7 +49738,7 @@
       </c>
       <c r="AA340" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO340" t="inlineStr">
@@ -50278,12 +49748,7 @@
       </c>
       <c r="AP340" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ340" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS340" t="inlineStr">
@@ -50293,11 +49758,6 @@
       </c>
       <c r="AT340" t="n">
         <v>1</v>
-      </c>
-      <c r="AU340" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV340" t="inlineStr">
         <is>
@@ -50559,17 +50019,15 @@
       <c r="O342" t="n">
         <v>0</v>
       </c>
+      <c r="P342" t="n">
+        <v>0</v>
+      </c>
       <c r="Q342" t="n">
         <v>0</v>
       </c>
       <c r="R342" t="n">
         <v>0</v>
       </c>
-      <c r="S342" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U342" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -50577,7 +50035,7 @@
       </c>
       <c r="AA342" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO342" t="inlineStr">
@@ -50587,12 +50045,7 @@
       </c>
       <c r="AP342" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ342" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS342" t="inlineStr">
@@ -50602,11 +50055,6 @@
       </c>
       <c r="AT342" t="n">
         <v>1</v>
-      </c>
-      <c r="AU342" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV342" t="inlineStr">
         <is>
@@ -51141,17 +50589,15 @@
       <c r="O346" t="n">
         <v>0</v>
       </c>
+      <c r="P346" t="n">
+        <v>0</v>
+      </c>
       <c r="Q346" t="n">
         <v>0</v>
       </c>
       <c r="R346" t="n">
         <v>0</v>
       </c>
-      <c r="S346" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U346" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -51159,7 +50605,7 @@
       </c>
       <c r="AA346" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO346" t="inlineStr">
@@ -51169,12 +50615,7 @@
       </c>
       <c r="AP346" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ346" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS346" t="inlineStr">
@@ -51184,11 +50625,6 @@
       </c>
       <c r="AT346" t="n">
         <v>1</v>
-      </c>
-      <c r="AU346" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV346" t="inlineStr">
         <is>
@@ -51450,17 +50886,15 @@
       <c r="O348" t="n">
         <v>0</v>
       </c>
+      <c r="P348" t="n">
+        <v>0</v>
+      </c>
       <c r="Q348" t="n">
         <v>0</v>
       </c>
       <c r="R348" t="n">
         <v>0</v>
       </c>
-      <c r="S348" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U348" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -51468,7 +50902,7 @@
       </c>
       <c r="AA348" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO348" t="inlineStr">
@@ -51478,12 +50912,7 @@
       </c>
       <c r="AP348" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ348" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS348" t="inlineStr">
@@ -51493,11 +50922,6 @@
       </c>
       <c r="AT348" t="n">
         <v>1</v>
-      </c>
-      <c r="AU348" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV348" t="inlineStr">
         <is>
@@ -51759,17 +51183,15 @@
       <c r="O350" t="n">
         <v>0</v>
       </c>
+      <c r="P350" t="n">
+        <v>0</v>
+      </c>
       <c r="Q350" t="n">
         <v>0</v>
       </c>
       <c r="R350" t="n">
         <v>0</v>
       </c>
-      <c r="S350" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U350" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -51777,7 +51199,7 @@
       </c>
       <c r="AA350" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO350" t="inlineStr">
@@ -51787,12 +51209,7 @@
       </c>
       <c r="AP350" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ350" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS350" t="inlineStr">
@@ -51802,11 +51219,6 @@
       </c>
       <c r="AT350" t="n">
         <v>1</v>
-      </c>
-      <c r="AU350" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV350" t="inlineStr">
         <is>
@@ -52068,17 +51480,15 @@
       <c r="O352" t="n">
         <v>0</v>
       </c>
+      <c r="P352" t="n">
+        <v>0</v>
+      </c>
       <c r="Q352" t="n">
         <v>0</v>
       </c>
       <c r="R352" t="n">
         <v>0</v>
       </c>
-      <c r="S352" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U352" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -52086,7 +51496,7 @@
       </c>
       <c r="AA352" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO352" t="inlineStr">
@@ -52096,12 +51506,7 @@
       </c>
       <c r="AP352" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ352" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS352" t="inlineStr">
@@ -52111,11 +51516,6 @@
       </c>
       <c r="AT352" t="n">
         <v>1</v>
-      </c>
-      <c r="AU352" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV352" t="inlineStr">
         <is>
@@ -52377,17 +51777,15 @@
       <c r="O354" t="n">
         <v>0</v>
       </c>
+      <c r="P354" t="n">
+        <v>0</v>
+      </c>
       <c r="Q354" t="n">
         <v>0</v>
       </c>
       <c r="R354" t="n">
         <v>0</v>
       </c>
-      <c r="S354" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U354" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -52395,7 +51793,7 @@
       </c>
       <c r="AA354" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO354" t="inlineStr">
@@ -52405,12 +51803,7 @@
       </c>
       <c r="AP354" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ354" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS354" t="inlineStr">
@@ -52420,11 +51813,6 @@
       </c>
       <c r="AT354" t="n">
         <v>1</v>
-      </c>
-      <c r="AU354" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV354" t="inlineStr">
         <is>
@@ -52959,17 +52347,15 @@
       <c r="O358" t="n">
         <v>0</v>
       </c>
+      <c r="P358" t="n">
+        <v>0</v>
+      </c>
       <c r="Q358" t="n">
         <v>0</v>
       </c>
       <c r="R358" t="n">
         <v>0</v>
       </c>
-      <c r="S358" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U358" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -52977,7 +52363,7 @@
       </c>
       <c r="AA358" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO358" t="inlineStr">
@@ -52987,12 +52373,7 @@
       </c>
       <c r="AP358" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ358" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS358" t="inlineStr">
@@ -53002,11 +52383,6 @@
       </c>
       <c r="AT358" t="n">
         <v>1</v>
-      </c>
-      <c r="AU358" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV358" t="inlineStr">
         <is>
@@ -53268,17 +52644,15 @@
       <c r="O360" t="n">
         <v>0</v>
       </c>
+      <c r="P360" t="n">
+        <v>0</v>
+      </c>
       <c r="Q360" t="n">
         <v>0</v>
       </c>
       <c r="R360" t="n">
         <v>0</v>
       </c>
-      <c r="S360" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U360" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -53286,7 +52660,7 @@
       </c>
       <c r="AA360" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO360" t="inlineStr">
@@ -53296,12 +52670,7 @@
       </c>
       <c r="AP360" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ360" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS360" t="inlineStr">
@@ -53311,11 +52680,6 @@
       </c>
       <c r="AT360" t="n">
         <v>1</v>
-      </c>
-      <c r="AU360" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV360" t="inlineStr">
         <is>
@@ -53577,17 +52941,15 @@
       <c r="O362" t="n">
         <v>0</v>
       </c>
+      <c r="P362" t="n">
+        <v>0</v>
+      </c>
       <c r="Q362" t="n">
         <v>0</v>
       </c>
       <c r="R362" t="n">
         <v>0</v>
       </c>
-      <c r="S362" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U362" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -53595,7 +52957,7 @@
       </c>
       <c r="AA362" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO362" t="inlineStr">
@@ -53605,12 +52967,7 @@
       </c>
       <c r="AP362" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ362" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS362" t="inlineStr">
@@ -53620,11 +52977,6 @@
       </c>
       <c r="AT362" t="n">
         <v>1</v>
-      </c>
-      <c r="AU362" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV362" t="inlineStr">
         <is>
@@ -53886,17 +53238,15 @@
       <c r="O364" t="n">
         <v>0</v>
       </c>
+      <c r="P364" t="n">
+        <v>0</v>
+      </c>
       <c r="Q364" t="n">
         <v>0</v>
       </c>
       <c r="R364" t="n">
         <v>0</v>
       </c>
-      <c r="S364" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U364" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -53904,7 +53254,7 @@
       </c>
       <c r="AA364" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO364" t="inlineStr">
@@ -53914,12 +53264,7 @@
       </c>
       <c r="AP364" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ364" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS364" t="inlineStr">
@@ -53929,11 +53274,6 @@
       </c>
       <c r="AT364" t="n">
         <v>1</v>
-      </c>
-      <c r="AU364" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV364" t="inlineStr">
         <is>
@@ -54468,17 +53808,15 @@
       <c r="O368" t="n">
         <v>0</v>
       </c>
+      <c r="P368" t="n">
+        <v>0</v>
+      </c>
       <c r="Q368" t="n">
         <v>0</v>
       </c>
       <c r="R368" t="n">
         <v>0</v>
       </c>
-      <c r="S368" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U368" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -54486,7 +53824,7 @@
       </c>
       <c r="AA368" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO368" t="inlineStr">
@@ -54496,12 +53834,7 @@
       </c>
       <c r="AP368" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ368" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS368" t="inlineStr">
@@ -54511,11 +53844,6 @@
       </c>
       <c r="AT368" t="n">
         <v>1</v>
-      </c>
-      <c r="AU368" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV368" t="inlineStr">
         <is>
@@ -54777,17 +54105,15 @@
       <c r="O370" t="n">
         <v>0</v>
       </c>
+      <c r="P370" t="n">
+        <v>0</v>
+      </c>
       <c r="Q370" t="n">
         <v>0</v>
       </c>
       <c r="R370" t="n">
         <v>0</v>
       </c>
-      <c r="S370" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U370" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -54795,7 +54121,7 @@
       </c>
       <c r="AA370" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO370" t="inlineStr">
@@ -54805,12 +54131,7 @@
       </c>
       <c r="AP370" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ370" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS370" t="inlineStr">
@@ -54820,11 +54141,6 @@
       </c>
       <c r="AT370" t="n">
         <v>1</v>
-      </c>
-      <c r="AU370" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV370" t="inlineStr">
         <is>
@@ -55086,17 +54402,15 @@
       <c r="O372" t="n">
         <v>0</v>
       </c>
+      <c r="P372" t="n">
+        <v>0</v>
+      </c>
       <c r="Q372" t="n">
         <v>0</v>
       </c>
       <c r="R372" t="n">
         <v>0</v>
       </c>
-      <c r="S372" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U372" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -55104,7 +54418,7 @@
       </c>
       <c r="AA372" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO372" t="inlineStr">
@@ -55114,12 +54428,7 @@
       </c>
       <c r="AP372" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ372" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS372" t="inlineStr">
@@ -55129,11 +54438,6 @@
       </c>
       <c r="AT372" t="n">
         <v>1</v>
-      </c>
-      <c r="AU372" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV372" t="inlineStr">
         <is>
@@ -55395,17 +54699,15 @@
       <c r="O374" t="n">
         <v>0</v>
       </c>
+      <c r="P374" t="n">
+        <v>0</v>
+      </c>
       <c r="Q374" t="n">
         <v>0</v>
       </c>
       <c r="R374" t="n">
         <v>0</v>
       </c>
-      <c r="S374" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U374" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -55413,7 +54715,7 @@
       </c>
       <c r="AA374" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO374" t="inlineStr">
@@ -55423,12 +54725,7 @@
       </c>
       <c r="AP374" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ374" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS374" t="inlineStr">
@@ -55438,11 +54735,6 @@
       </c>
       <c r="AT374" t="n">
         <v>1</v>
-      </c>
-      <c r="AU374" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV374" t="inlineStr">
         <is>
@@ -55842,17 +55134,15 @@
       <c r="O377" t="n">
         <v>0</v>
       </c>
+      <c r="P377" t="n">
+        <v>0</v>
+      </c>
       <c r="Q377" t="n">
         <v>0</v>
       </c>
       <c r="R377" t="n">
         <v>0</v>
       </c>
-      <c r="S377" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U377" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -55860,7 +55150,7 @@
       </c>
       <c r="AA377" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO377" t="inlineStr">
@@ -55870,12 +55160,7 @@
       </c>
       <c r="AP377" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ377" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS377" t="inlineStr">
@@ -55885,11 +55170,6 @@
       </c>
       <c r="AT377" t="n">
         <v>1</v>
-      </c>
-      <c r="AU377" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV377" t="inlineStr">
         <is>
@@ -56286,17 +55566,15 @@
       <c r="O380" t="n">
         <v>0</v>
       </c>
+      <c r="P380" t="n">
+        <v>0</v>
+      </c>
       <c r="Q380" t="n">
         <v>0</v>
       </c>
       <c r="R380" t="n">
         <v>0</v>
       </c>
-      <c r="S380" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U380" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -56304,7 +55582,7 @@
       </c>
       <c r="AA380" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO380" t="inlineStr">
@@ -56314,12 +55592,7 @@
       </c>
       <c r="AP380" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ380" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS380" t="inlineStr">
@@ -56329,11 +55602,6 @@
       </c>
       <c r="AT380" t="n">
         <v>1</v>
-      </c>
-      <c r="AU380" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV380" t="inlineStr">
         <is>
@@ -56595,17 +55863,15 @@
       <c r="O382" t="n">
         <v>0</v>
       </c>
+      <c r="P382" t="n">
+        <v>0</v>
+      </c>
       <c r="Q382" t="n">
         <v>0</v>
       </c>
       <c r="R382" t="n">
         <v>0</v>
       </c>
-      <c r="S382" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U382" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -56613,7 +55879,7 @@
       </c>
       <c r="AA382" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO382" t="inlineStr">
@@ -56623,12 +55889,7 @@
       </c>
       <c r="AP382" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ382" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS382" t="inlineStr">
@@ -56638,11 +55899,6 @@
       </c>
       <c r="AT382" t="n">
         <v>1</v>
-      </c>
-      <c r="AU382" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV382" t="inlineStr">
         <is>
@@ -56904,17 +56160,15 @@
       <c r="O384" t="n">
         <v>0</v>
       </c>
+      <c r="P384" t="n">
+        <v>0</v>
+      </c>
       <c r="Q384" t="n">
         <v>0</v>
       </c>
       <c r="R384" t="n">
         <v>0</v>
       </c>
-      <c r="S384" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U384" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -56922,7 +56176,7 @@
       </c>
       <c r="AA384" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO384" t="inlineStr">
@@ -56932,12 +56186,7 @@
       </c>
       <c r="AP384" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ384" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS384" t="inlineStr">
@@ -56947,11 +56196,6 @@
       </c>
       <c r="AT384" t="n">
         <v>1</v>
-      </c>
-      <c r="AU384" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV384" t="inlineStr">
         <is>
@@ -57213,17 +56457,15 @@
       <c r="O386" t="n">
         <v>0</v>
       </c>
+      <c r="P386" t="n">
+        <v>0</v>
+      </c>
       <c r="Q386" t="n">
         <v>0</v>
       </c>
       <c r="R386" t="n">
         <v>0</v>
       </c>
-      <c r="S386" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U386" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -57231,7 +56473,7 @@
       </c>
       <c r="AA386" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO386" t="inlineStr">
@@ -57241,12 +56483,7 @@
       </c>
       <c r="AP386" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ386" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS386" t="inlineStr">
@@ -57256,11 +56493,6 @@
       </c>
       <c r="AT386" t="n">
         <v>1</v>
-      </c>
-      <c r="AU386" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV386" t="inlineStr">
         <is>
@@ -57795,17 +57027,15 @@
       <c r="O390" t="n">
         <v>0</v>
       </c>
+      <c r="P390" t="n">
+        <v>0</v>
+      </c>
       <c r="Q390" t="n">
         <v>0</v>
       </c>
       <c r="R390" t="n">
         <v>0</v>
       </c>
-      <c r="S390" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U390" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -57813,7 +57043,7 @@
       </c>
       <c r="AA390" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO390" t="inlineStr">
@@ -57823,12 +57053,7 @@
       </c>
       <c r="AP390" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ390" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS390" t="inlineStr">
@@ -57838,11 +57063,6 @@
       </c>
       <c r="AT390" t="n">
         <v>1</v>
-      </c>
-      <c r="AU390" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV390" t="inlineStr">
         <is>
@@ -58104,17 +57324,15 @@
       <c r="O392" t="n">
         <v>0</v>
       </c>
+      <c r="P392" t="n">
+        <v>0</v>
+      </c>
       <c r="Q392" t="n">
         <v>0</v>
       </c>
       <c r="R392" t="n">
         <v>0</v>
       </c>
-      <c r="S392" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U392" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -58122,7 +57340,7 @@
       </c>
       <c r="AA392" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO392" t="inlineStr">
@@ -58132,12 +57350,7 @@
       </c>
       <c r="AP392" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ392" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS392" t="inlineStr">
@@ -58147,11 +57360,6 @@
       </c>
       <c r="AT392" t="n">
         <v>1</v>
-      </c>
-      <c r="AU392" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV392" t="inlineStr">
         <is>
@@ -58413,17 +57621,15 @@
       <c r="O394" t="n">
         <v>0</v>
       </c>
+      <c r="P394" t="n">
+        <v>0</v>
+      </c>
       <c r="Q394" t="n">
         <v>0</v>
       </c>
       <c r="R394" t="n">
         <v>0</v>
       </c>
-      <c r="S394" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U394" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -58431,7 +57637,7 @@
       </c>
       <c r="AA394" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO394" t="inlineStr">
@@ -58441,12 +57647,7 @@
       </c>
       <c r="AP394" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ394" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS394" t="inlineStr">
@@ -58456,11 +57657,6 @@
       </c>
       <c r="AT394" t="n">
         <v>1</v>
-      </c>
-      <c r="AU394" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV394" t="inlineStr">
         <is>
@@ -58722,17 +57918,15 @@
       <c r="O396" t="n">
         <v>0</v>
       </c>
+      <c r="P396" t="n">
+        <v>0</v>
+      </c>
       <c r="Q396" t="n">
         <v>0</v>
       </c>
       <c r="R396" t="n">
         <v>0</v>
       </c>
-      <c r="S396" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U396" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -58740,7 +57934,7 @@
       </c>
       <c r="AA396" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO396" t="inlineStr">
@@ -58750,12 +57944,7 @@
       </c>
       <c r="AP396" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ396" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS396" t="inlineStr">
@@ -58765,11 +57954,6 @@
       </c>
       <c r="AT396" t="n">
         <v>1</v>
-      </c>
-      <c r="AU396" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV396" t="inlineStr">
         <is>
@@ -64164,17 +63348,15 @@
       <c r="O433" t="n">
         <v>0</v>
       </c>
+      <c r="P433" t="n">
+        <v>0</v>
+      </c>
       <c r="Q433" t="n">
         <v>0</v>
       </c>
       <c r="R433" t="n">
         <v>0</v>
       </c>
-      <c r="S433" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U433" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -64182,7 +63364,7 @@
       </c>
       <c r="AA433" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO433" t="inlineStr">
@@ -64192,12 +63374,7 @@
       </c>
       <c r="AP433" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ433" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS433" t="inlineStr">
@@ -64207,11 +63384,6 @@
       </c>
       <c r="AT433" t="n">
         <v>1</v>
-      </c>
-      <c r="AU433" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV433" t="inlineStr">
         <is>
@@ -64473,17 +63645,15 @@
       <c r="O435" t="n">
         <v>0</v>
       </c>
+      <c r="P435" t="n">
+        <v>0</v>
+      </c>
       <c r="Q435" t="n">
         <v>0</v>
       </c>
       <c r="R435" t="n">
         <v>0</v>
       </c>
-      <c r="S435" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U435" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -64491,7 +63661,7 @@
       </c>
       <c r="AA435" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO435" t="inlineStr">
@@ -64501,12 +63671,7 @@
       </c>
       <c r="AP435" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ435" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS435" t="inlineStr">
@@ -64516,11 +63681,6 @@
       </c>
       <c r="AT435" t="n">
         <v>1</v>
-      </c>
-      <c r="AU435" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV435" t="inlineStr">
         <is>
@@ -64782,17 +63942,15 @@
       <c r="O437" t="n">
         <v>0</v>
       </c>
+      <c r="P437" t="n">
+        <v>0</v>
+      </c>
       <c r="Q437" t="n">
         <v>0</v>
       </c>
       <c r="R437" t="n">
         <v>0</v>
       </c>
-      <c r="S437" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U437" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -64800,7 +63958,7 @@
       </c>
       <c r="AA437" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO437" t="inlineStr">
@@ -64810,12 +63968,7 @@
       </c>
       <c r="AP437" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ437" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS437" t="inlineStr">
@@ -64825,11 +63978,6 @@
       </c>
       <c r="AT437" t="n">
         <v>1</v>
-      </c>
-      <c r="AU437" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV437" t="inlineStr">
         <is>
@@ -65091,17 +64239,15 @@
       <c r="O439" t="n">
         <v>0</v>
       </c>
+      <c r="P439" t="n">
+        <v>0</v>
+      </c>
       <c r="Q439" t="n">
         <v>0</v>
       </c>
       <c r="R439" t="n">
         <v>0</v>
       </c>
-      <c r="S439" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U439" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -65109,7 +64255,7 @@
       </c>
       <c r="AA439" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO439" t="inlineStr">
@@ -65119,12 +64265,7 @@
       </c>
       <c r="AP439" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ439" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS439" t="inlineStr">
@@ -65134,11 +64275,6 @@
       </c>
       <c r="AT439" t="n">
         <v>1</v>
-      </c>
-      <c r="AU439" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV439" t="inlineStr">
         <is>
@@ -65400,17 +64536,15 @@
       <c r="O441" t="n">
         <v>0</v>
       </c>
+      <c r="P441" t="n">
+        <v>0</v>
+      </c>
       <c r="Q441" t="n">
         <v>0</v>
       </c>
       <c r="R441" t="n">
         <v>0</v>
       </c>
-      <c r="S441" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U441" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -65418,7 +64552,7 @@
       </c>
       <c r="AA441" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO441" t="inlineStr">
@@ -65428,12 +64562,7 @@
       </c>
       <c r="AP441" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ441" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS441" t="inlineStr">
@@ -65443,11 +64572,6 @@
       </c>
       <c r="AT441" t="n">
         <v>1</v>
-      </c>
-      <c r="AU441" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV441" t="inlineStr">
         <is>
@@ -65982,17 +65106,15 @@
       <c r="O445" t="n">
         <v>0</v>
       </c>
+      <c r="P445" t="n">
+        <v>0</v>
+      </c>
       <c r="Q445" t="n">
         <v>0</v>
       </c>
       <c r="R445" t="n">
         <v>0</v>
       </c>
-      <c r="S445" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U445" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -66000,7 +65122,7 @@
       </c>
       <c r="AA445" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO445" t="inlineStr">
@@ -66010,12 +65132,7 @@
       </c>
       <c r="AP445" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ445" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS445" t="inlineStr">
@@ -66025,11 +65142,6 @@
       </c>
       <c r="AT445" t="n">
         <v>1</v>
-      </c>
-      <c r="AU445" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV445" t="inlineStr">
         <is>
@@ -66291,17 +65403,15 @@
       <c r="O447" t="n">
         <v>0</v>
       </c>
+      <c r="P447" t="n">
+        <v>0</v>
+      </c>
       <c r="Q447" t="n">
         <v>0</v>
       </c>
       <c r="R447" t="n">
         <v>0</v>
       </c>
-      <c r="S447" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U447" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -66309,7 +65419,7 @@
       </c>
       <c r="AA447" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO447" t="inlineStr">
@@ -66319,12 +65429,7 @@
       </c>
       <c r="AP447" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ447" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS447" t="inlineStr">
@@ -66334,11 +65439,6 @@
       </c>
       <c r="AT447" t="n">
         <v>1</v>
-      </c>
-      <c r="AU447" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV447" t="inlineStr">
         <is>
@@ -66600,17 +65700,15 @@
       <c r="O449" t="n">
         <v>0</v>
       </c>
+      <c r="P449" t="n">
+        <v>0</v>
+      </c>
       <c r="Q449" t="n">
         <v>0</v>
       </c>
       <c r="R449" t="n">
         <v>0</v>
       </c>
-      <c r="S449" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U449" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -66618,7 +65716,7 @@
       </c>
       <c r="AA449" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO449" t="inlineStr">
@@ -66628,12 +65726,7 @@
       </c>
       <c r="AP449" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ449" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS449" t="inlineStr">
@@ -66643,11 +65736,6 @@
       </c>
       <c r="AT449" t="n">
         <v>1</v>
-      </c>
-      <c r="AU449" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV449" t="inlineStr">
         <is>
@@ -66909,17 +65997,15 @@
       <c r="O451" t="n">
         <v>0</v>
       </c>
+      <c r="P451" t="n">
+        <v>0</v>
+      </c>
       <c r="Q451" t="n">
         <v>0</v>
       </c>
       <c r="R451" t="n">
         <v>0</v>
       </c>
-      <c r="S451" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U451" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -66927,7 +66013,7 @@
       </c>
       <c r="AA451" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO451" t="inlineStr">
@@ -66937,12 +66023,7 @@
       </c>
       <c r="AP451" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ451" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS451" t="inlineStr">
@@ -66952,11 +66033,6 @@
       </c>
       <c r="AT451" t="n">
         <v>1</v>
-      </c>
-      <c r="AU451" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV451" t="inlineStr">
         <is>
@@ -67491,17 +66567,15 @@
       <c r="O455" t="n">
         <v>0</v>
       </c>
+      <c r="P455" t="n">
+        <v>0</v>
+      </c>
       <c r="Q455" t="n">
         <v>0</v>
       </c>
       <c r="R455" t="n">
         <v>0</v>
       </c>
-      <c r="S455" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U455" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -67509,7 +66583,7 @@
       </c>
       <c r="AA455" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO455" t="inlineStr">
@@ -67519,12 +66593,7 @@
       </c>
       <c r="AP455" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ455" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS455" t="inlineStr">
@@ -67534,11 +66603,6 @@
       </c>
       <c r="AT455" t="n">
         <v>1</v>
-      </c>
-      <c r="AU455" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV455" t="inlineStr">
         <is>
@@ -67800,17 +66864,15 @@
       <c r="O457" t="n">
         <v>0</v>
       </c>
+      <c r="P457" t="n">
+        <v>0</v>
+      </c>
       <c r="Q457" t="n">
         <v>0</v>
       </c>
       <c r="R457" t="n">
         <v>0</v>
       </c>
-      <c r="S457" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U457" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -67818,7 +66880,7 @@
       </c>
       <c r="AA457" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO457" t="inlineStr">
@@ -67828,12 +66890,7 @@
       </c>
       <c r="AP457" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ457" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS457" t="inlineStr">
@@ -67843,11 +66900,6 @@
       </c>
       <c r="AT457" t="n">
         <v>1</v>
-      </c>
-      <c r="AU457" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV457" t="inlineStr">
         <is>
@@ -68109,17 +67161,15 @@
       <c r="O459" t="n">
         <v>0</v>
       </c>
+      <c r="P459" t="n">
+        <v>0</v>
+      </c>
       <c r="Q459" t="n">
         <v>0</v>
       </c>
       <c r="R459" t="n">
         <v>0</v>
       </c>
-      <c r="S459" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U459" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -68127,7 +67177,7 @@
       </c>
       <c r="AA459" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO459" t="inlineStr">
@@ -68137,12 +67187,7 @@
       </c>
       <c r="AP459" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ459" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS459" t="inlineStr">
@@ -68152,11 +67197,6 @@
       </c>
       <c r="AT459" t="n">
         <v>1</v>
-      </c>
-      <c r="AU459" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV459" t="inlineStr">
         <is>
@@ -68418,17 +67458,15 @@
       <c r="O461" t="n">
         <v>0</v>
       </c>
+      <c r="P461" t="n">
+        <v>0</v>
+      </c>
       <c r="Q461" t="n">
         <v>0</v>
       </c>
       <c r="R461" t="n">
         <v>0</v>
       </c>
-      <c r="S461" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U461" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -68436,7 +67474,7 @@
       </c>
       <c r="AA461" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO461" t="inlineStr">
@@ -68446,12 +67484,7 @@
       </c>
       <c r="AP461" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ461" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS461" t="inlineStr">
@@ -68461,11 +67494,6 @@
       </c>
       <c r="AT461" t="n">
         <v>1</v>
-      </c>
-      <c r="AU461" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV461" t="inlineStr">
         <is>
@@ -69000,17 +68028,15 @@
       <c r="O465" t="n">
         <v>0</v>
       </c>
+      <c r="P465" t="n">
+        <v>0</v>
+      </c>
       <c r="Q465" t="n">
         <v>0</v>
       </c>
       <c r="R465" t="n">
         <v>0</v>
       </c>
-      <c r="S465" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U465" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -69018,7 +68044,7 @@
       </c>
       <c r="AA465" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO465" t="inlineStr">
@@ -69028,12 +68054,7 @@
       </c>
       <c r="AP465" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ465" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS465" t="inlineStr">
@@ -69043,11 +68064,6 @@
       </c>
       <c r="AT465" t="n">
         <v>1</v>
-      </c>
-      <c r="AU465" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV465" t="inlineStr">
         <is>
@@ -69309,17 +68325,15 @@
       <c r="O467" t="n">
         <v>0</v>
       </c>
+      <c r="P467" t="n">
+        <v>0</v>
+      </c>
       <c r="Q467" t="n">
         <v>0</v>
       </c>
       <c r="R467" t="n">
         <v>0</v>
       </c>
-      <c r="S467" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U467" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -69327,7 +68341,7 @@
       </c>
       <c r="AA467" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO467" t="inlineStr">
@@ -69337,12 +68351,7 @@
       </c>
       <c r="AP467" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ467" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS467" t="inlineStr">
@@ -69352,11 +68361,6 @@
       </c>
       <c r="AT467" t="n">
         <v>1</v>
-      </c>
-      <c r="AU467" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV467" t="inlineStr">
         <is>
@@ -69618,17 +68622,15 @@
       <c r="O469" t="n">
         <v>0</v>
       </c>
+      <c r="P469" t="n">
+        <v>0</v>
+      </c>
       <c r="Q469" t="n">
         <v>0</v>
       </c>
       <c r="R469" t="n">
         <v>0</v>
       </c>
-      <c r="S469" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U469" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -69636,7 +68638,7 @@
       </c>
       <c r="AA469" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO469" t="inlineStr">
@@ -69646,12 +68648,7 @@
       </c>
       <c r="AP469" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ469" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS469" t="inlineStr">
@@ -69661,11 +68658,6 @@
       </c>
       <c r="AT469" t="n">
         <v>1</v>
-      </c>
-      <c r="AU469" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV469" t="inlineStr">
         <is>
@@ -69927,17 +68919,15 @@
       <c r="O471" t="n">
         <v>0</v>
       </c>
+      <c r="P471" t="n">
+        <v>0</v>
+      </c>
       <c r="Q471" t="n">
         <v>0</v>
       </c>
       <c r="R471" t="n">
         <v>0</v>
       </c>
-      <c r="S471" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U471" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -69945,7 +68935,7 @@
       </c>
       <c r="AA471" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO471" t="inlineStr">
@@ -69955,12 +68945,7 @@
       </c>
       <c r="AP471" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ471" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS471" t="inlineStr">
@@ -69970,11 +68955,6 @@
       </c>
       <c r="AT471" t="n">
         <v>1</v>
-      </c>
-      <c r="AU471" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV471" t="inlineStr">
         <is>
@@ -70509,17 +69489,15 @@
       <c r="O475" t="n">
         <v>0</v>
       </c>
+      <c r="P475" t="n">
+        <v>0</v>
+      </c>
       <c r="Q475" t="n">
         <v>0</v>
       </c>
       <c r="R475" t="n">
         <v>0</v>
       </c>
-      <c r="S475" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U475" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -70527,7 +69505,7 @@
       </c>
       <c r="AA475" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO475" t="inlineStr">
@@ -70537,12 +69515,7 @@
       </c>
       <c r="AP475" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ475" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS475" t="inlineStr">
@@ -70552,11 +69525,6 @@
       </c>
       <c r="AT475" t="n">
         <v>1</v>
-      </c>
-      <c r="AU475" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV475" t="inlineStr">
         <is>
@@ -70818,17 +69786,15 @@
       <c r="O477" t="n">
         <v>0</v>
       </c>
+      <c r="P477" t="n">
+        <v>0</v>
+      </c>
       <c r="Q477" t="n">
         <v>0</v>
       </c>
       <c r="R477" t="n">
         <v>0</v>
       </c>
-      <c r="S477" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U477" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -70836,7 +69802,7 @@
       </c>
       <c r="AA477" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO477" t="inlineStr">
@@ -70846,12 +69812,7 @@
       </c>
       <c r="AP477" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ477" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS477" t="inlineStr">
@@ -70861,11 +69822,6 @@
       </c>
       <c r="AT477" t="n">
         <v>1</v>
-      </c>
-      <c r="AU477" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV477" t="inlineStr">
         <is>
@@ -71127,17 +70083,15 @@
       <c r="O479" t="n">
         <v>0</v>
       </c>
+      <c r="P479" t="n">
+        <v>0</v>
+      </c>
       <c r="Q479" t="n">
         <v>0</v>
       </c>
       <c r="R479" t="n">
         <v>0</v>
       </c>
-      <c r="S479" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U479" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -71145,7 +70099,7 @@
       </c>
       <c r="AA479" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO479" t="inlineStr">
@@ -71155,12 +70109,7 @@
       </c>
       <c r="AP479" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ479" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS479" t="inlineStr">
@@ -71170,11 +70119,6 @@
       </c>
       <c r="AT479" t="n">
         <v>1</v>
-      </c>
-      <c r="AU479" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV479" t="inlineStr">
         <is>
@@ -71436,17 +70380,15 @@
       <c r="O481" t="n">
         <v>0</v>
       </c>
+      <c r="P481" t="n">
+        <v>0</v>
+      </c>
       <c r="Q481" t="n">
         <v>0</v>
       </c>
       <c r="R481" t="n">
         <v>0</v>
       </c>
-      <c r="S481" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U481" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -71454,7 +70396,7 @@
       </c>
       <c r="AA481" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO481" t="inlineStr">
@@ -71464,12 +70406,7 @@
       </c>
       <c r="AP481" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ481" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS481" t="inlineStr">
@@ -71479,11 +70416,6 @@
       </c>
       <c r="AT481" t="n">
         <v>1</v>
-      </c>
-      <c r="AU481" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV481" t="inlineStr">
         <is>
@@ -71745,17 +70677,15 @@
       <c r="O483" t="n">
         <v>0</v>
       </c>
+      <c r="P483" t="n">
+        <v>0</v>
+      </c>
       <c r="Q483" t="n">
         <v>0</v>
       </c>
       <c r="R483" t="n">
         <v>0</v>
       </c>
-      <c r="S483" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U483" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -71763,7 +70693,7 @@
       </c>
       <c r="AA483" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO483" t="inlineStr">
@@ -71773,12 +70703,7 @@
       </c>
       <c r="AP483" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ483" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS483" t="inlineStr">
@@ -71788,11 +70713,6 @@
       </c>
       <c r="AT483" t="n">
         <v>1</v>
-      </c>
-      <c r="AU483" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV483" t="inlineStr">
         <is>
@@ -72327,17 +71247,15 @@
       <c r="O487" t="n">
         <v>0</v>
       </c>
+      <c r="P487" t="n">
+        <v>0</v>
+      </c>
       <c r="Q487" t="n">
         <v>0</v>
       </c>
       <c r="R487" t="n">
         <v>0</v>
       </c>
-      <c r="S487" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U487" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -72345,7 +71263,7 @@
       </c>
       <c r="AA487" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO487" t="inlineStr">
@@ -72355,12 +71273,7 @@
       </c>
       <c r="AP487" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ487" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS487" t="inlineStr">
@@ -72370,11 +71283,6 @@
       </c>
       <c r="AT487" t="n">
         <v>1</v>
-      </c>
-      <c r="AU487" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV487" t="inlineStr">
         <is>
@@ -72636,17 +71544,15 @@
       <c r="O489" t="n">
         <v>0</v>
       </c>
+      <c r="P489" t="n">
+        <v>0</v>
+      </c>
       <c r="Q489" t="n">
         <v>0</v>
       </c>
       <c r="R489" t="n">
         <v>0</v>
       </c>
-      <c r="S489" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U489" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -72654,7 +71560,7 @@
       </c>
       <c r="AA489" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO489" t="inlineStr">
@@ -72664,12 +71570,7 @@
       </c>
       <c r="AP489" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ489" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS489" t="inlineStr">
@@ -72679,11 +71580,6 @@
       </c>
       <c r="AT489" t="n">
         <v>1</v>
-      </c>
-      <c r="AU489" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV489" t="inlineStr">
         <is>
@@ -72945,17 +71841,15 @@
       <c r="O491" t="n">
         <v>0</v>
       </c>
+      <c r="P491" t="n">
+        <v>0</v>
+      </c>
       <c r="Q491" t="n">
         <v>0</v>
       </c>
       <c r="R491" t="n">
         <v>0</v>
       </c>
-      <c r="S491" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U491" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -72963,7 +71857,7 @@
       </c>
       <c r="AA491" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO491" t="inlineStr">
@@ -72973,12 +71867,7 @@
       </c>
       <c r="AP491" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ491" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS491" t="inlineStr">
@@ -72988,11 +71877,6 @@
       </c>
       <c r="AT491" t="n">
         <v>1</v>
-      </c>
-      <c r="AU491" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV491" t="inlineStr">
         <is>
@@ -73254,17 +72138,15 @@
       <c r="O493" t="n">
         <v>0</v>
       </c>
+      <c r="P493" t="n">
+        <v>0</v>
+      </c>
       <c r="Q493" t="n">
         <v>0</v>
       </c>
       <c r="R493" t="n">
         <v>0</v>
       </c>
-      <c r="S493" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U493" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -73272,7 +72154,7 @@
       </c>
       <c r="AA493" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO493" t="inlineStr">
@@ -73282,12 +72164,7 @@
       </c>
       <c r="AP493" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ493" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS493" t="inlineStr">
@@ -73297,11 +72174,6 @@
       </c>
       <c r="AT493" t="n">
         <v>1</v>
-      </c>
-      <c r="AU493" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV493" t="inlineStr">
         <is>
@@ -73836,17 +72708,15 @@
       <c r="O497" t="n">
         <v>0</v>
       </c>
+      <c r="P497" t="n">
+        <v>0</v>
+      </c>
       <c r="Q497" t="n">
         <v>0</v>
       </c>
       <c r="R497" t="n">
         <v>0</v>
       </c>
-      <c r="S497" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U497" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -73854,7 +72724,7 @@
       </c>
       <c r="AA497" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO497" t="inlineStr">
@@ -73864,12 +72734,7 @@
       </c>
       <c r="AP497" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ497" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS497" t="inlineStr">
@@ -73879,11 +72744,6 @@
       </c>
       <c r="AT497" t="n">
         <v>1</v>
-      </c>
-      <c r="AU497" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV497" t="inlineStr">
         <is>
@@ -74145,17 +73005,15 @@
       <c r="O499" t="n">
         <v>0</v>
       </c>
+      <c r="P499" t="n">
+        <v>0</v>
+      </c>
       <c r="Q499" t="n">
         <v>0</v>
       </c>
       <c r="R499" t="n">
         <v>0</v>
       </c>
-      <c r="S499" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U499" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -74163,7 +73021,7 @@
       </c>
       <c r="AA499" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO499" t="inlineStr">
@@ -74173,12 +73031,7 @@
       </c>
       <c r="AP499" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ499" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS499" t="inlineStr">
@@ -74188,11 +73041,6 @@
       </c>
       <c r="AT499" t="n">
         <v>1</v>
-      </c>
-      <c r="AU499" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV499" t="inlineStr">
         <is>
@@ -74454,17 +73302,15 @@
       <c r="O501" t="n">
         <v>0</v>
       </c>
+      <c r="P501" t="n">
+        <v>0</v>
+      </c>
       <c r="Q501" t="n">
         <v>0</v>
       </c>
       <c r="R501" t="n">
         <v>0</v>
       </c>
-      <c r="S501" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U501" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -74472,7 +73318,7 @@
       </c>
       <c r="AA501" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO501" t="inlineStr">
@@ -74482,12 +73328,7 @@
       </c>
       <c r="AP501" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ501" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS501" t="inlineStr">
@@ -74497,11 +73338,6 @@
       </c>
       <c r="AT501" t="n">
         <v>1</v>
-      </c>
-      <c r="AU501" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV501" t="inlineStr">
         <is>
@@ -74763,17 +73599,15 @@
       <c r="O503" t="n">
         <v>0</v>
       </c>
+      <c r="P503" t="n">
+        <v>0</v>
+      </c>
       <c r="Q503" t="n">
         <v>0</v>
       </c>
       <c r="R503" t="n">
         <v>0</v>
       </c>
-      <c r="S503" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U503" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -74781,7 +73615,7 @@
       </c>
       <c r="AA503" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO503" t="inlineStr">
@@ -74791,12 +73625,7 @@
       </c>
       <c r="AP503" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ503" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS503" t="inlineStr">
@@ -74806,11 +73635,6 @@
       </c>
       <c r="AT503" t="n">
         <v>1</v>
-      </c>
-      <c r="AU503" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV503" t="inlineStr">
         <is>
@@ -75210,17 +74034,15 @@
       <c r="O506" t="n">
         <v>0</v>
       </c>
+      <c r="P506" t="n">
+        <v>0</v>
+      </c>
       <c r="Q506" t="n">
         <v>0</v>
       </c>
       <c r="R506" t="n">
         <v>0</v>
       </c>
-      <c r="S506" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U506" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -75228,7 +74050,7 @@
       </c>
       <c r="AA506" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO506" t="inlineStr">
@@ -75238,12 +74060,7 @@
       </c>
       <c r="AP506" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ506" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS506" t="inlineStr">
@@ -75253,11 +74070,6 @@
       </c>
       <c r="AT506" t="n">
         <v>1</v>
-      </c>
-      <c r="AU506" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV506" t="inlineStr">
         <is>
@@ -75654,17 +74466,15 @@
       <c r="O509" t="n">
         <v>0</v>
       </c>
+      <c r="P509" t="n">
+        <v>0</v>
+      </c>
       <c r="Q509" t="n">
         <v>0</v>
       </c>
       <c r="R509" t="n">
         <v>0</v>
       </c>
-      <c r="S509" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U509" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -75672,7 +74482,7 @@
       </c>
       <c r="AA509" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO509" t="inlineStr">
@@ -75682,12 +74492,7 @@
       </c>
       <c r="AP509" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ509" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS509" t="inlineStr">
@@ -75697,11 +74502,6 @@
       </c>
       <c r="AT509" t="n">
         <v>1</v>
-      </c>
-      <c r="AU509" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV509" t="inlineStr">
         <is>
@@ -75963,17 +74763,15 @@
       <c r="O511" t="n">
         <v>0</v>
       </c>
+      <c r="P511" t="n">
+        <v>0</v>
+      </c>
       <c r="Q511" t="n">
         <v>0</v>
       </c>
       <c r="R511" t="n">
         <v>0</v>
       </c>
-      <c r="S511" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U511" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -75981,7 +74779,7 @@
       </c>
       <c r="AA511" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO511" t="inlineStr">
@@ -75991,12 +74789,7 @@
       </c>
       <c r="AP511" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ511" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS511" t="inlineStr">
@@ -76006,11 +74799,6 @@
       </c>
       <c r="AT511" t="n">
         <v>1</v>
-      </c>
-      <c r="AU511" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV511" t="inlineStr">
         <is>
@@ -76272,17 +75060,15 @@
       <c r="O513" t="n">
         <v>0</v>
       </c>
+      <c r="P513" t="n">
+        <v>0</v>
+      </c>
       <c r="Q513" t="n">
         <v>0</v>
       </c>
       <c r="R513" t="n">
         <v>0</v>
       </c>
-      <c r="S513" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U513" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -76290,7 +75076,7 @@
       </c>
       <c r="AA513" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO513" t="inlineStr">
@@ -76300,12 +75086,7 @@
       </c>
       <c r="AP513" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ513" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS513" t="inlineStr">
@@ -76315,11 +75096,6 @@
       </c>
       <c r="AT513" t="n">
         <v>1</v>
-      </c>
-      <c r="AU513" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV513" t="inlineStr">
         <is>
@@ -76581,17 +75357,15 @@
       <c r="O515" t="n">
         <v>0</v>
       </c>
+      <c r="P515" t="n">
+        <v>0</v>
+      </c>
       <c r="Q515" t="n">
         <v>0</v>
       </c>
       <c r="R515" t="n">
         <v>0</v>
       </c>
-      <c r="S515" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U515" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -76599,7 +75373,7 @@
       </c>
       <c r="AA515" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO515" t="inlineStr">
@@ -76609,12 +75383,7 @@
       </c>
       <c r="AP515" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ515" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS515" t="inlineStr">
@@ -76624,11 +75393,6 @@
       </c>
       <c r="AT515" t="n">
         <v>1</v>
-      </c>
-      <c r="AU515" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV515" t="inlineStr">
         <is>
@@ -77163,17 +75927,15 @@
       <c r="O519" t="n">
         <v>0</v>
       </c>
+      <c r="P519" t="n">
+        <v>0</v>
+      </c>
       <c r="Q519" t="n">
         <v>0</v>
       </c>
       <c r="R519" t="n">
         <v>0</v>
       </c>
-      <c r="S519" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U519" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -77181,7 +75943,7 @@
       </c>
       <c r="AA519" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO519" t="inlineStr">
@@ -77191,12 +75953,7 @@
       </c>
       <c r="AP519" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ519" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS519" t="inlineStr">
@@ -77206,11 +75963,6 @@
       </c>
       <c r="AT519" t="n">
         <v>1</v>
-      </c>
-      <c r="AU519" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV519" t="inlineStr">
         <is>
@@ -77472,17 +76224,15 @@
       <c r="O521" t="n">
         <v>0</v>
       </c>
+      <c r="P521" t="n">
+        <v>0</v>
+      </c>
       <c r="Q521" t="n">
         <v>0</v>
       </c>
       <c r="R521" t="n">
         <v>0</v>
       </c>
-      <c r="S521" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U521" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -77490,7 +76240,7 @@
       </c>
       <c r="AA521" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO521" t="inlineStr">
@@ -77500,12 +76250,7 @@
       </c>
       <c r="AP521" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ521" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS521" t="inlineStr">
@@ -77515,11 +76260,6 @@
       </c>
       <c r="AT521" t="n">
         <v>1</v>
-      </c>
-      <c r="AU521" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV521" t="inlineStr">
         <is>
@@ -77781,17 +76521,15 @@
       <c r="O523" t="n">
         <v>0</v>
       </c>
+      <c r="P523" t="n">
+        <v>0</v>
+      </c>
       <c r="Q523" t="n">
         <v>0</v>
       </c>
       <c r="R523" t="n">
         <v>0</v>
       </c>
-      <c r="S523" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U523" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -77799,7 +76537,7 @@
       </c>
       <c r="AA523" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO523" t="inlineStr">
@@ -77809,12 +76547,7 @@
       </c>
       <c r="AP523" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ523" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS523" t="inlineStr">
@@ -77824,11 +76557,6 @@
       </c>
       <c r="AT523" t="n">
         <v>1</v>
-      </c>
-      <c r="AU523" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV523" t="inlineStr">
         <is>
@@ -78090,17 +76818,15 @@
       <c r="O525" t="n">
         <v>0</v>
       </c>
+      <c r="P525" t="n">
+        <v>0</v>
+      </c>
       <c r="Q525" t="n">
         <v>0</v>
       </c>
       <c r="R525" t="n">
         <v>0</v>
       </c>
-      <c r="S525" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U525" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -78108,7 +76834,7 @@
       </c>
       <c r="AA525" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO525" t="inlineStr">
@@ -78118,12 +76844,7 @@
       </c>
       <c r="AP525" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ525" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS525" t="inlineStr">
@@ -78133,11 +76854,6 @@
       </c>
       <c r="AT525" t="n">
         <v>1</v>
-      </c>
-      <c r="AU525" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV525" t="inlineStr">
         <is>
@@ -78672,17 +77388,15 @@
       <c r="O529" t="n">
         <v>0</v>
       </c>
+      <c r="P529" t="n">
+        <v>0</v>
+      </c>
       <c r="Q529" t="n">
         <v>0</v>
       </c>
       <c r="R529" t="n">
         <v>0</v>
       </c>
-      <c r="S529" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U529" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -78690,7 +77404,7 @@
       </c>
       <c r="AA529" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO529" t="inlineStr">
@@ -78700,12 +77414,7 @@
       </c>
       <c r="AP529" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ529" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS529" t="inlineStr">
@@ -78715,11 +77424,6 @@
       </c>
       <c r="AT529" t="n">
         <v>1</v>
-      </c>
-      <c r="AU529" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV529" t="inlineStr">
         <is>
@@ -78981,17 +77685,15 @@
       <c r="O531" t="n">
         <v>0</v>
       </c>
+      <c r="P531" t="n">
+        <v>0</v>
+      </c>
       <c r="Q531" t="n">
         <v>0</v>
       </c>
       <c r="R531" t="n">
         <v>0</v>
       </c>
-      <c r="S531" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U531" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -78999,7 +77701,7 @@
       </c>
       <c r="AA531" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO531" t="inlineStr">
@@ -79009,12 +77711,7 @@
       </c>
       <c r="AP531" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ531" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS531" t="inlineStr">
@@ -79024,11 +77721,6 @@
       </c>
       <c r="AT531" t="n">
         <v>1</v>
-      </c>
-      <c r="AU531" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV531" t="inlineStr">
         <is>
@@ -79290,17 +77982,15 @@
       <c r="O533" t="n">
         <v>0</v>
       </c>
+      <c r="P533" t="n">
+        <v>0</v>
+      </c>
       <c r="Q533" t="n">
         <v>0</v>
       </c>
       <c r="R533" t="n">
         <v>0</v>
       </c>
-      <c r="S533" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U533" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -79308,7 +77998,7 @@
       </c>
       <c r="AA533" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO533" t="inlineStr">
@@ -79318,12 +78008,7 @@
       </c>
       <c r="AP533" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ533" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS533" t="inlineStr">
@@ -79333,11 +78018,6 @@
       </c>
       <c r="AT533" t="n">
         <v>1</v>
-      </c>
-      <c r="AU533" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV533" t="inlineStr">
         <is>
@@ -79599,17 +78279,15 @@
       <c r="O535" t="n">
         <v>0</v>
       </c>
+      <c r="P535" t="n">
+        <v>0</v>
+      </c>
       <c r="Q535" t="n">
         <v>0</v>
       </c>
       <c r="R535" t="n">
         <v>0</v>
       </c>
-      <c r="S535" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U535" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -79617,7 +78295,7 @@
       </c>
       <c r="AA535" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO535" t="inlineStr">
@@ -79627,12 +78305,7 @@
       </c>
       <c r="AP535" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ535" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS535" t="inlineStr">
@@ -79642,11 +78315,6 @@
       </c>
       <c r="AT535" t="n">
         <v>1</v>
-      </c>
-      <c r="AU535" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV535" t="inlineStr">
         <is>
@@ -79908,17 +78576,15 @@
       <c r="O537" t="n">
         <v>0</v>
       </c>
+      <c r="P537" t="n">
+        <v>0</v>
+      </c>
       <c r="Q537" t="n">
         <v>0</v>
       </c>
       <c r="R537" t="n">
         <v>0</v>
       </c>
-      <c r="S537" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U537" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -79926,7 +78592,7 @@
       </c>
       <c r="AA537" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO537" t="inlineStr">
@@ -79936,12 +78602,7 @@
       </c>
       <c r="AP537" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ537" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS537" t="inlineStr">
@@ -79951,11 +78612,6 @@
       </c>
       <c r="AT537" t="n">
         <v>1</v>
-      </c>
-      <c r="AU537" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV537" t="inlineStr">
         <is>
@@ -80490,17 +79146,15 @@
       <c r="O541" t="n">
         <v>0</v>
       </c>
+      <c r="P541" t="n">
+        <v>0</v>
+      </c>
       <c r="Q541" t="n">
         <v>0</v>
       </c>
       <c r="R541" t="n">
         <v>0</v>
       </c>
-      <c r="S541" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U541" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -80508,7 +79162,7 @@
       </c>
       <c r="AA541" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO541" t="inlineStr">
@@ -80518,12 +79172,7 @@
       </c>
       <c r="AP541" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ541" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS541" t="inlineStr">
@@ -80533,11 +79182,6 @@
       </c>
       <c r="AT541" t="n">
         <v>1</v>
-      </c>
-      <c r="AU541" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV541" t="inlineStr">
         <is>
@@ -80799,17 +79443,15 @@
       <c r="O543" t="n">
         <v>0</v>
       </c>
+      <c r="P543" t="n">
+        <v>0</v>
+      </c>
       <c r="Q543" t="n">
         <v>0</v>
       </c>
       <c r="R543" t="n">
         <v>0</v>
       </c>
-      <c r="S543" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U543" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -80817,7 +79459,7 @@
       </c>
       <c r="AA543" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO543" t="inlineStr">
@@ -80827,12 +79469,7 @@
       </c>
       <c r="AP543" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ543" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS543" t="inlineStr">
@@ -80842,11 +79479,6 @@
       </c>
       <c r="AT543" t="n">
         <v>1</v>
-      </c>
-      <c r="AU543" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV543" t="inlineStr">
         <is>
@@ -81108,17 +79740,15 @@
       <c r="O545" t="n">
         <v>0</v>
       </c>
+      <c r="P545" t="n">
+        <v>0</v>
+      </c>
       <c r="Q545" t="n">
         <v>0</v>
       </c>
       <c r="R545" t="n">
         <v>0</v>
       </c>
-      <c r="S545" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U545" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -81126,7 +79756,7 @@
       </c>
       <c r="AA545" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO545" t="inlineStr">
@@ -81136,12 +79766,7 @@
       </c>
       <c r="AP545" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ545" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS545" t="inlineStr">
@@ -81151,11 +79776,6 @@
       </c>
       <c r="AT545" t="n">
         <v>1</v>
-      </c>
-      <c r="AU545" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV545" t="inlineStr">
         <is>
@@ -81417,17 +80037,15 @@
       <c r="O547" t="n">
         <v>0</v>
       </c>
+      <c r="P547" t="n">
+        <v>0</v>
+      </c>
       <c r="Q547" t="n">
         <v>0</v>
       </c>
       <c r="R547" t="n">
         <v>0</v>
       </c>
-      <c r="S547" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U547" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -81435,7 +80053,7 @@
       </c>
       <c r="AA547" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO547" t="inlineStr">
@@ -81445,12 +80063,7 @@
       </c>
       <c r="AP547" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ547" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS547" t="inlineStr">
@@ -81460,11 +80073,6 @@
       </c>
       <c r="AT547" t="n">
         <v>1</v>
-      </c>
-      <c r="AU547" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV547" t="inlineStr">
         <is>
@@ -81999,17 +80607,15 @@
       <c r="O551" t="n">
         <v>0</v>
       </c>
+      <c r="P551" t="n">
+        <v>0</v>
+      </c>
       <c r="Q551" t="n">
         <v>0</v>
       </c>
       <c r="R551" t="n">
         <v>0</v>
       </c>
-      <c r="S551" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U551" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -82017,7 +80623,7 @@
       </c>
       <c r="AA551" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO551" t="inlineStr">
@@ -82027,12 +80633,7 @@
       </c>
       <c r="AP551" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ551" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS551" t="inlineStr">
@@ -82042,11 +80643,6 @@
       </c>
       <c r="AT551" t="n">
         <v>1</v>
-      </c>
-      <c r="AU551" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV551" t="inlineStr">
         <is>
@@ -82308,17 +80904,15 @@
       <c r="O553" t="n">
         <v>0</v>
       </c>
+      <c r="P553" t="n">
+        <v>0</v>
+      </c>
       <c r="Q553" t="n">
         <v>0</v>
       </c>
       <c r="R553" t="n">
         <v>0</v>
       </c>
-      <c r="S553" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U553" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -82326,7 +80920,7 @@
       </c>
       <c r="AA553" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO553" t="inlineStr">
@@ -82336,12 +80930,7 @@
       </c>
       <c r="AP553" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ553" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS553" t="inlineStr">
@@ -82351,11 +80940,6 @@
       </c>
       <c r="AT553" t="n">
         <v>1</v>
-      </c>
-      <c r="AU553" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV553" t="inlineStr">
         <is>
@@ -82617,17 +81201,15 @@
       <c r="O555" t="n">
         <v>0</v>
       </c>
+      <c r="P555" t="n">
+        <v>0</v>
+      </c>
       <c r="Q555" t="n">
         <v>0</v>
       </c>
       <c r="R555" t="n">
         <v>0</v>
       </c>
-      <c r="S555" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U555" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -82635,7 +81217,7 @@
       </c>
       <c r="AA555" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO555" t="inlineStr">
@@ -82645,12 +81227,7 @@
       </c>
       <c r="AP555" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ555" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS555" t="inlineStr">
@@ -82660,11 +81237,6 @@
       </c>
       <c r="AT555" t="n">
         <v>1</v>
-      </c>
-      <c r="AU555" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV555" t="inlineStr">
         <is>
@@ -82926,17 +81498,15 @@
       <c r="O557" t="n">
         <v>0</v>
       </c>
+      <c r="P557" t="n">
+        <v>0</v>
+      </c>
       <c r="Q557" t="n">
         <v>0</v>
       </c>
       <c r="R557" t="n">
         <v>0</v>
       </c>
-      <c r="S557" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U557" t="inlineStr">
         <is>
           <t>HOLD_JP_2bd005905c32c1242f113f0b78e2</t>
@@ -82944,7 +81514,7 @@
       </c>
       <c r="AA557" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO557" t="inlineStr">
@@ -82954,12 +81524,7 @@
       </c>
       <c r="AP557" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ557" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS557" t="inlineStr">
@@ -82969,11 +81534,6 @@
       </c>
       <c r="AT557" t="n">
         <v>1</v>
-      </c>
-      <c r="AU557" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV557" t="inlineStr">
         <is>
